--- a/reports/pdf_change_20261006.xlsx
+++ b/reports/pdf_change_20261006.xlsx
@@ -541,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K23"/>
+  <dimension ref="A1:K25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -567,14 +567,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>캡처 2/7  ·  대기: TIME, TIME, PLUS, RISE, TIGER</t>
+          <t>캡처 4/7  ·  대기: PLUS, RISE, TIGER</t>
         </is>
       </c>
     </row>
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 5,330억   ·   현금 9억(0.2%)      당일 2026-10-06  vs  전영업일 2026-10-02      매수 2종목  /  매도 5종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 5,330억      당일 2026-10-06  vs  전영업일 2026-10-02      매수 2종목  /  매도 5종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -835,7 +835,7 @@
     <row r="12" ht="19" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,475억   ·   현금 22억(0.6%)      당일 2026-10-06  vs  전영업일 2026-10-02      매수 0종목  /  매도 0종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,475억      당일 2026-10-06  vs  전영업일 2026-10-02      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B12" s="4" t="n"/>
@@ -857,60 +857,57 @@
       </c>
     </row>
     <row r="15" ht="19" customHeight="1">
-      <c r="A15" s="19" t="inlineStr">
-        <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B15" s="20" t="n"/>
-      <c r="C15" s="20" t="n"/>
-      <c r="D15" s="20" t="n"/>
-      <c r="E15" s="20" t="n"/>
-      <c r="F15" s="20" t="n"/>
-      <c r="G15" s="20" t="n"/>
-      <c r="H15" s="20" t="n"/>
-      <c r="I15" s="20" t="n"/>
-      <c r="J15" s="20" t="n"/>
-      <c r="K15" s="20" t="n"/>
-    </row>
-    <row r="17" ht="19" customHeight="1">
-      <c r="A17" s="19" t="inlineStr">
-        <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B17" s="20" t="n"/>
-      <c r="C17" s="20" t="n"/>
-      <c r="D17" s="20" t="n"/>
-      <c r="E17" s="20" t="n"/>
-      <c r="F17" s="20" t="n"/>
-      <c r="G17" s="20" t="n"/>
-      <c r="H17" s="20" t="n"/>
-      <c r="I17" s="20" t="n"/>
-      <c r="J17" s="20" t="n"/>
-      <c r="K17" s="20" t="n"/>
-    </row>
-    <row r="19" ht="19" customHeight="1">
-      <c r="A19" s="19" t="inlineStr">
-        <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B19" s="20" t="n"/>
-      <c r="C19" s="20" t="n"/>
-      <c r="D19" s="20" t="n"/>
-      <c r="E19" s="20" t="n"/>
-      <c r="F19" s="20" t="n"/>
-      <c r="G19" s="20" t="n"/>
-      <c r="H19" s="20" t="n"/>
-      <c r="I19" s="20" t="n"/>
-      <c r="J19" s="20" t="n"/>
-      <c r="K19" s="20" t="n"/>
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,868억   ·   현금 42억(1.5%)      당일 2026-10-06  vs  전영업일 2026-10-02      매수 0종목  /  매도 0종목</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="n"/>
+      <c r="C15" s="4" t="n"/>
+      <c r="D15" s="4" t="n"/>
+      <c r="E15" s="4" t="n"/>
+      <c r="F15" s="4" t="n"/>
+      <c r="G15" s="4" t="n"/>
+      <c r="H15" s="4" t="n"/>
+      <c r="I15" s="4" t="n"/>
+      <c r="J15" s="4" t="n"/>
+      <c r="K15" s="4" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="18" t="inlineStr">
+        <is>
+          <t>변화 없음 (구성종목 동일)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="19" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,140억   ·   현금 9억(0.4%)      당일 2026-10-06  vs  전영업일 2026-10-02      매수 0종목  /  매도 0종목</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="n"/>
+      <c r="C18" s="4" t="n"/>
+      <c r="D18" s="4" t="n"/>
+      <c r="E18" s="4" t="n"/>
+      <c r="F18" s="4" t="n"/>
+      <c r="G18" s="4" t="n"/>
+      <c r="H18" s="4" t="n"/>
+      <c r="I18" s="4" t="n"/>
+      <c r="J18" s="4" t="n"/>
+      <c r="K18" s="4" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="18" t="inlineStr">
+        <is>
+          <t>변화 없음 (구성종목 동일)</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="19" customHeight="1">
       <c r="A21" s="19" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
         </is>
       </c>
       <c r="B21" s="20" t="n"/>
@@ -927,7 +924,7 @@
     <row r="23" ht="19" customHeight="1">
       <c r="A23" s="19" t="inlineStr">
         <is>
-          <t>■ TIGER 기술이전바이오액티브  (미래에셋)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
         </is>
       </c>
       <c r="B23" s="20" t="n"/>
@@ -941,19 +938,38 @@
       <c r="J23" s="20" t="n"/>
       <c r="K23" s="20" t="n"/>
     </row>
+    <row r="25" ht="19" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>■ TIGER 기술이전바이오액티브  (미래에셋)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
+        </is>
+      </c>
+      <c r="B25" s="20" t="n"/>
+      <c r="C25" s="20" t="n"/>
+      <c r="D25" s="20" t="n"/>
+      <c r="E25" s="20" t="n"/>
+      <c r="F25" s="20" t="n"/>
+      <c r="G25" s="20" t="n"/>
+      <c r="H25" s="20" t="n"/>
+      <c r="I25" s="20" t="n"/>
+      <c r="J25" s="20" t="n"/>
+      <c r="K25" s="20" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="14">
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="A12:K12"/>
+    <mergeCell ref="A18:K18"/>
     <mergeCell ref="A3:K3"/>
     <mergeCell ref="A21:K21"/>
-    <mergeCell ref="A23:K23"/>
     <mergeCell ref="A15:K15"/>
+    <mergeCell ref="A25:K25"/>
     <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A16:K16"/>
     <mergeCell ref="A19:K19"/>
     <mergeCell ref="A13:K13"/>
     <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A17:K17"/>
+    <mergeCell ref="A23:K23"/>
     <mergeCell ref="G4:K4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/reports/pdf_change_20261006.xlsx
+++ b/reports/pdf_change_20261006.xlsx
@@ -574,7 +574,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 5,330억      당일 2026-10-06  vs  전영업일 2026-10-02      매수 2종목  /  매도 5종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 5,293억      당일 2026-10-06  vs  전영업일 2026-10-02      매수 2종목  /  매도 5종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -670,7 +670,7 @@
         <v>40</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>3291071258</v>
+        <v>3287701484</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
         <v>-30</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-996983775</v>
+        <v>-995962949</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>29</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>1517094058</v>
+        <v>1515540684</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
@@ -728,14 +728,14 @@
       </c>
       <c r="G7" s="14" t="inlineStr">
         <is>
-          <t>코나아이</t>
+          <t>코나아이 ※</t>
         </is>
       </c>
       <c r="H7" s="15" t="n">
         <v>-21</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-772699026</v>
+        <v>-771907848</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
@@ -763,7 +763,7 @@
         <v>-18</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-513863884</v>
+        <v>-513337732</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         <v>-14</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-731023835</v>
+        <v>-730275330</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         <v>-5</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-1266359715</v>
+        <v>-1265063071</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
     <row r="12" ht="19" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,475억      당일 2026-10-06  vs  전영업일 2026-10-02      매수 0종목  /  매도 0종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,381억      당일 2026-10-06  vs  전영업일 2026-10-02      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B12" s="4" t="n"/>
@@ -859,7 +859,7 @@
     <row r="15" ht="19" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,868억   ·   현금 42억(1.5%)      당일 2026-10-06  vs  전영업일 2026-10-02      매수 0종목  /  매도 0종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,842억      당일 2026-10-06  vs  전영업일 2026-10-02      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B15" s="4" t="n"/>
@@ -883,7 +883,7 @@
     <row r="18" ht="19" customHeight="1">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,140억   ·   현금 9억(0.4%)      당일 2026-10-06  vs  전영업일 2026-10-02      매수 0종목  /  매도 0종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,093억      당일 2026-10-06  vs  전영업일 2026-10-02      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B18" s="4" t="n"/>

--- a/reports/pdf_change_20261006.xlsx
+++ b/reports/pdf_change_20261006.xlsx
@@ -541,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K25"/>
+  <dimension ref="A1:K30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -567,7 +567,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>캡처 4/7  ·  대기: PLUS, RISE, TIGER</t>
+          <t>캡처 5/7  ·  대기: RISE, TIGER</t>
         </is>
       </c>
     </row>
@@ -905,71 +905,261 @@
       </c>
     </row>
     <row r="21" ht="19" customHeight="1">
-      <c r="A21" s="19" t="inlineStr">
-        <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B21" s="20" t="n"/>
-      <c r="C21" s="20" t="n"/>
-      <c r="D21" s="20" t="n"/>
-      <c r="E21" s="20" t="n"/>
-      <c r="F21" s="20" t="n"/>
-      <c r="G21" s="20" t="n"/>
-      <c r="H21" s="20" t="n"/>
-      <c r="I21" s="20" t="n"/>
-      <c r="J21" s="20" t="n"/>
-      <c r="K21" s="20" t="n"/>
-    </row>
-    <row r="23" ht="19" customHeight="1">
-      <c r="A23" s="19" t="inlineStr">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 316억   ·   현금 2억(0.6%)      당일 2026-10-06  vs  전영업일 2026-10-02      매수 2종목  /  매도 3종목</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="n"/>
+      <c r="C21" s="4" t="n"/>
+      <c r="D21" s="4" t="n"/>
+      <c r="E21" s="4" t="n"/>
+      <c r="F21" s="4" t="n"/>
+      <c r="G21" s="4" t="n"/>
+      <c r="H21" s="4" t="n"/>
+      <c r="I21" s="4" t="n"/>
+      <c r="J21" s="4" t="n"/>
+      <c r="K21" s="4" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="n"/>
+      <c r="C22" s="6" t="n"/>
+      <c r="D22" s="6" t="n"/>
+      <c r="E22" s="6" t="n"/>
+      <c r="G22" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H22" s="8" t="n"/>
+      <c r="I22" s="8" t="n"/>
+      <c r="J22" s="8" t="n"/>
+      <c r="K22" s="8" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E23" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G23" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H23" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I23" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J23" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K23" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="inlineStr">
+        <is>
+          <t>필옵틱스  (신규)</t>
+        </is>
+      </c>
+      <c r="B24" s="11" t="n">
+        <v>34</v>
+      </c>
+      <c r="C24" s="11" t="n">
+        <v>94676372</v>
+      </c>
+      <c r="D24" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→0.30%</t>
+        </is>
+      </c>
+      <c r="E24" s="13" t="inlineStr">
+        <is>
+          <t>0→34</t>
+        </is>
+      </c>
+      <c r="G24" s="14" t="inlineStr">
+        <is>
+          <t>새로닉스</t>
+        </is>
+      </c>
+      <c r="H24" s="15" t="n">
+        <v>-109</v>
+      </c>
+      <c r="I24" s="15" t="n">
+        <v>-82569656</v>
+      </c>
+      <c r="J24" s="16" t="inlineStr">
+        <is>
+          <t>1.87%→1.61%</t>
+        </is>
+      </c>
+      <c r="K24" s="13" t="inlineStr">
+        <is>
+          <t>777→668</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="inlineStr">
+        <is>
+          <t>상신이디피</t>
+        </is>
+      </c>
+      <c r="B25" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="C25" s="11" t="n">
+        <v>21229594</v>
+      </c>
+      <c r="D25" s="12" t="inlineStr">
+        <is>
+          <t>2.34%→2.42%</t>
+        </is>
+      </c>
+      <c r="E25" s="13" t="inlineStr">
+        <is>
+          <t>487→501</t>
+        </is>
+      </c>
+      <c r="G25" s="14" t="inlineStr">
+        <is>
+          <t>두산테스나</t>
+        </is>
+      </c>
+      <c r="H25" s="15" t="n">
+        <v>-6</v>
+      </c>
+      <c r="I25" s="15" t="n">
+        <v>-43615187</v>
+      </c>
+      <c r="J25" s="16" t="inlineStr">
+        <is>
+          <t>2.22%→2.08%</t>
+        </is>
+      </c>
+      <c r="K25" s="13" t="inlineStr">
+        <is>
+          <t>96→90</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="17" t="n"/>
+      <c r="B26" s="17" t="n"/>
+      <c r="C26" s="17" t="n"/>
+      <c r="D26" s="17" t="n"/>
+      <c r="E26" s="17" t="n"/>
+      <c r="G26" s="14" t="inlineStr">
+        <is>
+          <t>테스</t>
+        </is>
+      </c>
+      <c r="H26" s="15" t="n">
+        <v>-3</v>
+      </c>
+      <c r="I26" s="15" t="n">
+        <v>-36189589</v>
+      </c>
+      <c r="J26" s="16" t="inlineStr">
+        <is>
+          <t>2.76%→2.65%</t>
+        </is>
+      </c>
+      <c r="K26" s="13" t="inlineStr">
+        <is>
+          <t>72→69</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="19" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
         <is>
           <t>■ RISE 바이오TOP10액티브  (KB)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
         </is>
       </c>
-      <c r="B23" s="20" t="n"/>
-      <c r="C23" s="20" t="n"/>
-      <c r="D23" s="20" t="n"/>
-      <c r="E23" s="20" t="n"/>
-      <c r="F23" s="20" t="n"/>
-      <c r="G23" s="20" t="n"/>
-      <c r="H23" s="20" t="n"/>
-      <c r="I23" s="20" t="n"/>
-      <c r="J23" s="20" t="n"/>
-      <c r="K23" s="20" t="n"/>
-    </row>
-    <row r="25" ht="19" customHeight="1">
-      <c r="A25" s="19" t="inlineStr">
+      <c r="B28" s="20" t="n"/>
+      <c r="C28" s="20" t="n"/>
+      <c r="D28" s="20" t="n"/>
+      <c r="E28" s="20" t="n"/>
+      <c r="F28" s="20" t="n"/>
+      <c r="G28" s="20" t="n"/>
+      <c r="H28" s="20" t="n"/>
+      <c r="I28" s="20" t="n"/>
+      <c r="J28" s="20" t="n"/>
+      <c r="K28" s="20" t="n"/>
+    </row>
+    <row r="30" ht="19" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
         <is>
           <t>■ TIGER 기술이전바이오액티브  (미래에셋)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
         </is>
       </c>
-      <c r="B25" s="20" t="n"/>
-      <c r="C25" s="20" t="n"/>
-      <c r="D25" s="20" t="n"/>
-      <c r="E25" s="20" t="n"/>
-      <c r="F25" s="20" t="n"/>
-      <c r="G25" s="20" t="n"/>
-      <c r="H25" s="20" t="n"/>
-      <c r="I25" s="20" t="n"/>
-      <c r="J25" s="20" t="n"/>
-      <c r="K25" s="20" t="n"/>
+      <c r="B30" s="20" t="n"/>
+      <c r="C30" s="20" t="n"/>
+      <c r="D30" s="20" t="n"/>
+      <c r="E30" s="20" t="n"/>
+      <c r="F30" s="20" t="n"/>
+      <c r="G30" s="20" t="n"/>
+      <c r="H30" s="20" t="n"/>
+      <c r="I30" s="20" t="n"/>
+      <c r="J30" s="20" t="n"/>
+      <c r="K30" s="20" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="16">
+    <mergeCell ref="G22:K22"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="A12:K12"/>
     <mergeCell ref="A18:K18"/>
     <mergeCell ref="A3:K3"/>
     <mergeCell ref="A21:K21"/>
+    <mergeCell ref="A30:K30"/>
     <mergeCell ref="A15:K15"/>
-    <mergeCell ref="A25:K25"/>
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="A16:K16"/>
     <mergeCell ref="A19:K19"/>
+    <mergeCell ref="A28:K28"/>
     <mergeCell ref="A13:K13"/>
+    <mergeCell ref="A22:E22"/>
     <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A23:K23"/>
     <mergeCell ref="G4:K4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/reports/pdf_change_20261006.xlsx
+++ b/reports/pdf_change_20261006.xlsx
@@ -907,7 +907,7 @@
     <row r="21" ht="19" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 316억   ·   현금 2억(0.6%)      당일 2026-10-06  vs  전영업일 2026-10-02      매수 2종목  /  매도 3종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 316억      당일 2026-10-06  vs  전영업일 2026-10-02      매수 2종목  /  매도 3종목</t>
         </is>
       </c>
       <c r="B21" s="4" t="n"/>
